--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>90802</v>
+        <v>90905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744680</v>
       </c>
       <c r="B2" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744680</v>
+        <v>122744695</v>
       </c>
       <c r="B2" t="n">
-        <v>91879</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gulåsen NV, Hls</t>
+          <t>Gulåsen NÖ, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623916</v>
+        <v>623629</v>
       </c>
       <c r="R2" t="n">
-        <v>6876035</v>
+        <v>6876253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,516 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122744680</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gulåsen NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>623916</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6876035</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122744715</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skabbåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>623908</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6876068</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grenar på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122744713</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skabbåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>623909</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6876063</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122744718</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75468</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skabbåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>623933</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6876042</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122744717</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skabbåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>623937</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6876039</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 51227-2023 artfynd.xlsx
+++ b/artfynd/A 51227-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744695</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744715</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744718</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,8 +1313,21 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744717</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>